--- a/PCB/Task 2/Ashik/GRIFFI power width.xlsx
+++ b/PCB/Task 2/Ashik/GRIFFI power width.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cc.lee\Projects\038NC-GRIFFI\For_Designer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\homeoffice\PCB\Task 2\Ashik\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63616AD-663B-4F2D-97C5-95525531226F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-28920" yWindow="615" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10mil" sheetId="1" r:id="rId1"/>
@@ -17,7 +18,7 @@
     <sheet name="Data" sheetId="3" r:id="rId3"/>
     <sheet name="工作表3" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,9 +32,6 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -1637,24 +1635,31 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="新細明體"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1665,6 +1670,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1746,8 +1756,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1755,14 +1766,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2039,46 +2051,46 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AG18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.69921875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.3984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.3984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="22.69921875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2176,7 +2188,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -2229,7 +2241,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:33">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -2282,7 +2294,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -2335,7 +2347,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:33">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -2354,7 +2366,7 @@
       <c r="J5" t="s">
         <v>366</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="9" t="s">
         <v>387</v>
       </c>
       <c r="N5" t="s">
@@ -2388,7 +2400,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:33">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -2441,7 +2453,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:33">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -2494,7 +2506,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:33">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -2547,8 +2559,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="1:33" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:33" ht="15.75" thickBot="1"/>
+    <row r="11" spans="1:33" ht="15.75" thickTop="1">
       <c r="A11" s="2"/>
       <c r="B11" s="3" t="s">
         <v>521</v>
@@ -2614,144 +2626,129 @@
         <v>521</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:33">
       <c r="A12" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5" t="s">
+      <c r="D12" t="s">
         <v>149</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5" t="s">
+      <c r="F12" t="s">
         <v>77</v>
       </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5" t="s">
+      <c r="H12" t="s">
         <v>113</v>
       </c>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5" t="s">
+      <c r="J12" t="s">
         <v>69</v>
       </c>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5" t="s">
+      <c r="L12" t="s">
         <v>157</v>
       </c>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5" t="s">
+      <c r="N12" t="s">
         <v>61</v>
       </c>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5" t="s">
+      <c r="P12" t="s">
         <v>165</v>
       </c>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5" t="s">
+      <c r="R12" t="s">
         <v>105</v>
       </c>
-      <c r="S12" s="5"/>
-      <c r="T12" s="5" t="s">
+      <c r="T12" t="s">
         <v>121</v>
       </c>
-      <c r="U12" s="5"/>
-      <c r="V12" s="5" t="s">
+      <c r="V12" t="s">
         <v>97</v>
       </c>
-      <c r="W12" s="5"/>
-      <c r="X12" s="5" t="s">
+      <c r="X12" t="s">
         <v>129</v>
       </c>
-      <c r="Y12" s="5"/>
-      <c r="Z12" s="5" t="s">
+      <c r="Z12" t="s">
         <v>53</v>
       </c>
-      <c r="AA12" s="5"/>
-      <c r="AB12" s="5" t="s">
+      <c r="AB12" t="s">
         <v>137</v>
       </c>
-      <c r="AC12" s="5"/>
-      <c r="AD12" s="5" t="s">
+      <c r="AD12" t="s">
         <v>89</v>
       </c>
-      <c r="AE12" s="5"/>
-      <c r="AF12" s="6" t="s">
+      <c r="AF12" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:33" ht="15.75" thickBot="1">
+      <c r="A13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8" t="s">
+      <c r="C13" s="7"/>
+      <c r="D13" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8" t="s">
+      <c r="E13" s="7"/>
+      <c r="F13" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8" t="s">
+      <c r="G13" s="7"/>
+      <c r="H13" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8" t="s">
+      <c r="I13" s="7"/>
+      <c r="J13" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8" t="s">
+      <c r="K13" s="7"/>
+      <c r="L13" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8" t="s">
+      <c r="M13" s="7"/>
+      <c r="N13" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8" t="s">
+      <c r="O13" s="7"/>
+      <c r="P13" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8" t="s">
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="S13" s="8"/>
-      <c r="T13" s="8" t="s">
+      <c r="S13" s="7"/>
+      <c r="T13" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="U13" s="8"/>
-      <c r="V13" s="8" t="s">
+      <c r="U13" s="7"/>
+      <c r="V13" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="W13" s="8"/>
-      <c r="X13" s="8" t="s">
+      <c r="W13" s="7"/>
+      <c r="X13" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="Y13" s="8"/>
-      <c r="Z13" s="8" t="s">
+      <c r="Y13" s="7"/>
+      <c r="Z13" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8" t="s">
+      <c r="AA13" s="7"/>
+      <c r="AB13" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="AC13" s="8"/>
-      <c r="AD13" s="8" t="s">
+      <c r="AC13" s="7"/>
+      <c r="AD13" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="AE13" s="8"/>
-      <c r="AF13" s="9" t="s">
+      <c r="AE13" s="7"/>
+      <c r="AF13" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:33" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="1:33" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:33" ht="16.5" thickTop="1" thickBot="1"/>
+    <row r="15" spans="1:33" ht="15.75" thickTop="1">
       <c r="A15" s="2"/>
       <c r="B15" s="3" t="s">
         <v>520</v>
@@ -2817,143 +2814,128 @@
         <v>520</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:33">
       <c r="A16" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5" t="s">
+      <c r="D16" t="s">
         <v>149</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5" t="s">
+      <c r="F16" t="s">
         <v>77</v>
       </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5" t="s">
+      <c r="H16" t="s">
         <v>113</v>
       </c>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5" t="s">
+      <c r="J16" t="s">
         <v>69</v>
       </c>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5" t="s">
+      <c r="L16" t="s">
         <v>157</v>
       </c>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5" t="s">
+      <c r="N16" t="s">
         <v>61</v>
       </c>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5" t="s">
+      <c r="P16" t="s">
         <v>165</v>
       </c>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5" t="s">
+      <c r="R16" t="s">
         <v>105</v>
       </c>
-      <c r="S16" s="5"/>
-      <c r="T16" s="5" t="s">
+      <c r="T16" t="s">
         <v>121</v>
       </c>
-      <c r="U16" s="5"/>
-      <c r="V16" s="5" t="s">
+      <c r="V16" t="s">
         <v>97</v>
       </c>
-      <c r="W16" s="5"/>
-      <c r="X16" s="5" t="s">
+      <c r="X16" t="s">
         <v>129</v>
       </c>
-      <c r="Y16" s="5"/>
-      <c r="Z16" s="5" t="s">
+      <c r="Z16" t="s">
         <v>53</v>
       </c>
-      <c r="AA16" s="5"/>
-      <c r="AB16" s="5" t="s">
+      <c r="AB16" t="s">
         <v>137</v>
       </c>
-      <c r="AC16" s="5"/>
-      <c r="AD16" s="5" t="s">
+      <c r="AD16" t="s">
         <v>89</v>
       </c>
-      <c r="AE16" s="5"/>
-      <c r="AF16" s="6" t="s">
+      <c r="AF16" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:32" ht="15.75" thickBot="1">
+      <c r="A17" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8" t="s">
+      <c r="C17" s="7"/>
+      <c r="D17" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8" t="s">
+      <c r="E17" s="7"/>
+      <c r="F17" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8" t="s">
+      <c r="G17" s="7"/>
+      <c r="H17" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8" t="s">
+      <c r="I17" s="7"/>
+      <c r="J17" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8" t="s">
+      <c r="K17" s="7"/>
+      <c r="L17" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8" t="s">
+      <c r="M17" s="7"/>
+      <c r="N17" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8" t="s">
+      <c r="O17" s="7"/>
+      <c r="P17" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8" t="s">
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8" t="s">
+      <c r="S17" s="7"/>
+      <c r="T17" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="U17" s="8"/>
-      <c r="V17" s="8" t="s">
+      <c r="U17" s="7"/>
+      <c r="V17" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="W17" s="8"/>
-      <c r="X17" s="8" t="s">
+      <c r="W17" s="7"/>
+      <c r="X17" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="Y17" s="8"/>
-      <c r="Z17" s="8" t="s">
+      <c r="Y17" s="7"/>
+      <c r="Z17" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="AA17" s="8"/>
-      <c r="AB17" s="8" t="s">
+      <c r="AA17" s="7"/>
+      <c r="AB17" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="AC17" s="8"/>
-      <c r="AD17" s="8" t="s">
+      <c r="AC17" s="7"/>
+      <c r="AD17" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="AE17" s="8"/>
-      <c r="AF17" s="9" t="s">
+      <c r="AE17" s="7"/>
+      <c r="AF17" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:32" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:32" ht="15.75" thickTop="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2961,46 +2943,46 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AG4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.3984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.3984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="22.69921875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3098,7 +3080,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33">
       <c r="A2" t="s">
         <v>515</v>
       </c>
@@ -3151,7 +3133,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:33">
       <c r="A3" t="s">
         <v>516</v>
       </c>
@@ -3204,7 +3186,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33">
       <c r="A4" t="s">
         <v>517</v>
       </c>
@@ -3264,9 +3246,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3274,23 +3256,23 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:V240"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.69921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.09765625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.3984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="22.69921875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22">
       <c r="A1" t="s">
         <v>43</v>
       </c>
@@ -3334,7 +3316,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22">
       <c r="A2" t="s">
         <v>44</v>
       </c>
@@ -3375,7 +3357,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -3416,7 +3398,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -3457,7 +3439,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -3498,7 +3480,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22">
       <c r="A6" t="s">
         <v>48</v>
       </c>
@@ -3539,7 +3521,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22">
       <c r="A7" t="s">
         <v>49</v>
       </c>
@@ -3580,7 +3562,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22">
       <c r="A8" t="s">
         <v>50</v>
       </c>
@@ -3621,7 +3603,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -3662,7 +3644,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22">
       <c r="E10" t="s">
         <v>61</v>
       </c>
@@ -3689,7 +3671,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22">
       <c r="E11" t="s">
         <v>62</v>
       </c>
@@ -3716,7 +3698,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22">
       <c r="E12" t="s">
         <v>63</v>
       </c>
@@ -3743,7 +3725,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22">
       <c r="E13" t="s">
         <v>64</v>
       </c>
@@ -3770,7 +3752,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22">
       <c r="E14" t="s">
         <v>65</v>
       </c>
@@ -3797,7 +3779,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22">
       <c r="E15" t="s">
         <v>66</v>
       </c>
@@ -3824,7 +3806,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22">
       <c r="E16" t="s">
         <v>67</v>
       </c>
@@ -3851,7 +3833,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="17" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="17" spans="5:22">
       <c r="E17" t="s">
         <v>68</v>
       </c>
@@ -3878,7 +3860,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="18" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="18" spans="5:22">
       <c r="E18" t="s">
         <v>69</v>
       </c>
@@ -3905,7 +3887,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="19" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="19" spans="5:22">
       <c r="E19" t="s">
         <v>70</v>
       </c>
@@ -3932,7 +3914,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="20" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="20" spans="5:22">
       <c r="E20" t="s">
         <v>71</v>
       </c>
@@ -3959,7 +3941,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="21" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="21" spans="5:22">
       <c r="E21" t="s">
         <v>72</v>
       </c>
@@ -3986,7 +3968,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="22" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="22" spans="5:22">
       <c r="E22" t="s">
         <v>73</v>
       </c>
@@ -4013,7 +3995,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="23" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="23" spans="5:22">
       <c r="E23" t="s">
         <v>74</v>
       </c>
@@ -4040,7 +4022,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="24" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="24" spans="5:22">
       <c r="E24" t="s">
         <v>75</v>
       </c>
@@ -4067,7 +4049,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="25" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="25" spans="5:22">
       <c r="E25" t="s">
         <v>76</v>
       </c>
@@ -4094,7 +4076,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="26" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="26" spans="5:22">
       <c r="E26" t="s">
         <v>77</v>
       </c>
@@ -4121,7 +4103,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="27" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="27" spans="5:22">
       <c r="E27" t="s">
         <v>78</v>
       </c>
@@ -4148,7 +4130,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="28" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="28" spans="5:22">
       <c r="E28" t="s">
         <v>79</v>
       </c>
@@ -4175,7 +4157,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="29" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="29" spans="5:22">
       <c r="E29" t="s">
         <v>80</v>
       </c>
@@ -4202,7 +4184,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="30" spans="5:22">
       <c r="E30" t="s">
         <v>81</v>
       </c>
@@ -4229,7 +4211,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="31" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="31" spans="5:22">
       <c r="E31" t="s">
         <v>82</v>
       </c>
@@ -4256,7 +4238,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="32" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="32" spans="5:22">
       <c r="E32" t="s">
         <v>83</v>
       </c>
@@ -4283,7 +4265,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:22">
       <c r="E33" t="s">
         <v>45</v>
       </c>
@@ -4310,7 +4292,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="34" spans="5:22">
       <c r="E34" t="s">
         <v>50</v>
       </c>
@@ -4337,7 +4319,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="35" spans="5:22">
       <c r="E35" t="s">
         <v>51</v>
       </c>
@@ -4364,7 +4346,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="36" spans="5:22">
       <c r="E36" t="s">
         <v>44</v>
       </c>
@@ -4391,7 +4373,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="37" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="37" spans="5:22">
       <c r="E37" t="s">
         <v>84</v>
       </c>
@@ -4418,7 +4400,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="38" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="38" spans="5:22">
       <c r="E38" t="s">
         <v>85</v>
       </c>
@@ -4445,7 +4427,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="39" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="39" spans="5:22">
       <c r="E39" t="s">
         <v>86</v>
       </c>
@@ -4472,7 +4454,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="40" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="40" spans="5:22">
       <c r="E40" t="s">
         <v>87</v>
       </c>
@@ -4499,7 +4481,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="41" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="41" spans="5:22">
       <c r="E41" t="s">
         <v>88</v>
       </c>
@@ -4526,7 +4508,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="42" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="42" spans="5:22">
       <c r="E42" t="s">
         <v>89</v>
       </c>
@@ -4553,7 +4535,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="43" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="43" spans="5:22">
       <c r="E43" t="s">
         <v>90</v>
       </c>
@@ -4580,7 +4562,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="44" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="44" spans="5:22">
       <c r="E44" t="s">
         <v>91</v>
       </c>
@@ -4607,7 +4589,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="45" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="45" spans="5:22">
       <c r="E45" t="s">
         <v>92</v>
       </c>
@@ -4634,7 +4616,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="46" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="46" spans="5:22">
       <c r="E46" t="s">
         <v>93</v>
       </c>
@@ -4661,7 +4643,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="47" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="47" spans="5:22">
       <c r="E47" t="s">
         <v>94</v>
       </c>
@@ -4688,7 +4670,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="48" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="48" spans="5:22">
       <c r="E48" t="s">
         <v>95</v>
       </c>
@@ -4715,7 +4697,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="49" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="49" spans="5:22">
       <c r="E49" t="s">
         <v>96</v>
       </c>
@@ -4742,7 +4724,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="50" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="50" spans="5:22">
       <c r="E50" t="s">
         <v>97</v>
       </c>
@@ -4769,7 +4751,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="51" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="51" spans="5:22">
       <c r="E51" t="s">
         <v>98</v>
       </c>
@@ -4796,7 +4778,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="52" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="52" spans="5:22">
       <c r="E52" t="s">
         <v>99</v>
       </c>
@@ -4823,7 +4805,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="53" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="53" spans="5:22">
       <c r="E53" t="s">
         <v>100</v>
       </c>
@@ -4850,7 +4832,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="54" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="54" spans="5:22">
       <c r="E54" t="s">
         <v>101</v>
       </c>
@@ -4877,7 +4859,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="55" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="55" spans="5:22">
       <c r="E55" t="s">
         <v>102</v>
       </c>
@@ -4904,7 +4886,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="56" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="56" spans="5:22">
       <c r="E56" t="s">
         <v>103</v>
       </c>
@@ -4931,7 +4913,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="57" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="57" spans="5:22">
       <c r="E57" t="s">
         <v>104</v>
       </c>
@@ -4958,7 +4940,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="58" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="58" spans="5:22">
       <c r="E58" t="s">
         <v>105</v>
       </c>
@@ -4985,7 +4967,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="59" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="59" spans="5:22">
       <c r="E59" t="s">
         <v>106</v>
       </c>
@@ -5012,7 +4994,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="60" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="60" spans="5:22">
       <c r="E60" t="s">
         <v>107</v>
       </c>
@@ -5039,7 +5021,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="61" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="61" spans="5:22">
       <c r="E61" t="s">
         <v>108</v>
       </c>
@@ -5066,7 +5048,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="62" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="62" spans="5:22">
       <c r="E62" t="s">
         <v>109</v>
       </c>
@@ -5093,7 +5075,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="63" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="63" spans="5:22">
       <c r="E63" t="s">
         <v>110</v>
       </c>
@@ -5120,7 +5102,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="64" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="64" spans="5:22">
       <c r="E64" t="s">
         <v>111</v>
       </c>
@@ -5147,7 +5129,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="65" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="65" spans="5:22">
       <c r="E65" t="s">
         <v>112</v>
       </c>
@@ -5174,7 +5156,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="66" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="66" spans="5:22">
       <c r="E66" t="s">
         <v>113</v>
       </c>
@@ -5201,7 +5183,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="67" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="67" spans="5:22">
       <c r="E67" t="s">
         <v>114</v>
       </c>
@@ -5228,7 +5210,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="68" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="68" spans="5:22">
       <c r="E68" t="s">
         <v>115</v>
       </c>
@@ -5255,7 +5237,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="69" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="69" spans="5:22">
       <c r="E69" t="s">
         <v>116</v>
       </c>
@@ -5282,7 +5264,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="70" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="70" spans="5:22">
       <c r="E70" t="s">
         <v>117</v>
       </c>
@@ -5309,7 +5291,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="71" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="71" spans="5:22">
       <c r="E71" t="s">
         <v>118</v>
       </c>
@@ -5336,7 +5318,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="72" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="72" spans="5:22">
       <c r="E72" t="s">
         <v>119</v>
       </c>
@@ -5363,7 +5345,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="73" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="73" spans="5:22">
       <c r="E73" t="s">
         <v>120</v>
       </c>
@@ -5390,7 +5372,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="74" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="74" spans="5:22">
       <c r="E74" t="s">
         <v>121</v>
       </c>
@@ -5417,7 +5399,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="75" spans="5:22">
       <c r="E75" t="s">
         <v>122</v>
       </c>
@@ -5444,7 +5426,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="76" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="76" spans="5:22">
       <c r="E76" t="s">
         <v>123</v>
       </c>
@@ -5471,7 +5453,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="77" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="77" spans="5:22">
       <c r="E77" t="s">
         <v>124</v>
       </c>
@@ -5498,7 +5480,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="78" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="78" spans="5:22">
       <c r="E78" t="s">
         <v>125</v>
       </c>
@@ -5525,7 +5507,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="79" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="79" spans="5:22">
       <c r="E79" t="s">
         <v>126</v>
       </c>
@@ -5552,7 +5534,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="80" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="80" spans="5:22">
       <c r="E80" t="s">
         <v>127</v>
       </c>
@@ -5579,7 +5561,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="81" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="81" spans="5:22">
       <c r="E81" t="s">
         <v>128</v>
       </c>
@@ -5606,7 +5588,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="82" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="82" spans="5:22">
       <c r="E82" t="s">
         <v>129</v>
       </c>
@@ -5633,7 +5615,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="83" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="83" spans="5:22">
       <c r="E83" t="s">
         <v>130</v>
       </c>
@@ -5660,7 +5642,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="84" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="84" spans="5:22">
       <c r="E84" t="s">
         <v>131</v>
       </c>
@@ -5687,7 +5669,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="85" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="85" spans="5:22">
       <c r="E85" t="s">
         <v>132</v>
       </c>
@@ -5714,7 +5696,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="86" spans="5:22">
       <c r="E86" t="s">
         <v>133</v>
       </c>
@@ -5741,7 +5723,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="87" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="87" spans="5:22">
       <c r="E87" t="s">
         <v>134</v>
       </c>
@@ -5768,7 +5750,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="88" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="88" spans="5:22">
       <c r="E88" t="s">
         <v>135</v>
       </c>
@@ -5795,7 +5777,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="89" spans="5:22">
       <c r="E89" t="s">
         <v>136</v>
       </c>
@@ -5822,7 +5804,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="90" spans="5:22">
       <c r="E90" t="s">
         <v>137</v>
       </c>
@@ -5849,7 +5831,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="91" spans="5:22">
       <c r="E91" t="s">
         <v>138</v>
       </c>
@@ -5876,7 +5858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="92" spans="5:22">
       <c r="E92" t="s">
         <v>139</v>
       </c>
@@ -5903,7 +5885,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="93" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="93" spans="5:22">
       <c r="E93" t="s">
         <v>140</v>
       </c>
@@ -5930,7 +5912,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="94" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="94" spans="5:22">
       <c r="E94" t="s">
         <v>141</v>
       </c>
@@ -5957,7 +5939,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="95" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="95" spans="5:22">
       <c r="E95" t="s">
         <v>142</v>
       </c>
@@ -5984,7 +5966,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="96" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="96" spans="5:22">
       <c r="E96" t="s">
         <v>143</v>
       </c>
@@ -6011,7 +5993,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="97" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="97" spans="5:22">
       <c r="E97" t="s">
         <v>3</v>
       </c>
@@ -6038,7 +6020,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="98" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="98" spans="5:22">
       <c r="E98" t="s">
         <v>8</v>
       </c>
@@ -6065,7 +6047,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="99" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="99" spans="5:22">
       <c r="E99" t="s">
         <v>9</v>
       </c>
@@ -6092,7 +6074,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="100" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="100" spans="5:22">
       <c r="E100" t="s">
         <v>2</v>
       </c>
@@ -6119,7 +6101,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="101" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="101" spans="5:22">
       <c r="E101" t="s">
         <v>144</v>
       </c>
@@ -6146,7 +6128,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="102" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="102" spans="5:22">
       <c r="E102" t="s">
         <v>145</v>
       </c>
@@ -6173,7 +6155,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="103" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="103" spans="5:22">
       <c r="E103" t="s">
         <v>146</v>
       </c>
@@ -6200,7 +6182,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="104" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="104" spans="5:22">
       <c r="E104" t="s">
         <v>147</v>
       </c>
@@ -6227,7 +6209,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="105" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="105" spans="5:22">
       <c r="E105" t="s">
         <v>148</v>
       </c>
@@ -6254,7 +6236,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="106" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="106" spans="5:22">
       <c r="E106" t="s">
         <v>149</v>
       </c>
@@ -6281,7 +6263,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="107" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="107" spans="5:22">
       <c r="E107" t="s">
         <v>150</v>
       </c>
@@ -6308,7 +6290,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="108" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="108" spans="5:22">
       <c r="E108" t="s">
         <v>151</v>
       </c>
@@ -6335,7 +6317,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="109" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="109" spans="5:22">
       <c r="E109" t="s">
         <v>152</v>
       </c>
@@ -6362,7 +6344,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="110" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="110" spans="5:22">
       <c r="E110" t="s">
         <v>153</v>
       </c>
@@ -6389,7 +6371,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="111" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="111" spans="5:22">
       <c r="E111" t="s">
         <v>154</v>
       </c>
@@ -6416,7 +6398,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="112" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="112" spans="5:22">
       <c r="E112" t="s">
         <v>155</v>
       </c>
@@ -6443,7 +6425,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="113" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="113" spans="5:22">
       <c r="E113" t="s">
         <v>156</v>
       </c>
@@ -6464,7 +6446,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="114" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="114" spans="5:22">
       <c r="E114" t="s">
         <v>157</v>
       </c>
@@ -6485,7 +6467,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="115" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="115" spans="5:22">
       <c r="E115" t="s">
         <v>158</v>
       </c>
@@ -6506,7 +6488,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="116" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="116" spans="5:22">
       <c r="E116" t="s">
         <v>159</v>
       </c>
@@ -6527,7 +6509,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="117" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="117" spans="5:22">
       <c r="E117" t="s">
         <v>160</v>
       </c>
@@ -6548,7 +6530,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="118" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="118" spans="5:22">
       <c r="E118" t="s">
         <v>161</v>
       </c>
@@ -6569,7 +6551,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="119" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="119" spans="5:22">
       <c r="E119" t="s">
         <v>162</v>
       </c>
@@ -6590,7 +6572,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="120" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="120" spans="5:22">
       <c r="E120" t="s">
         <v>163</v>
       </c>
@@ -6611,7 +6593,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="121" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="121" spans="5:22">
       <c r="E121" t="s">
         <v>164</v>
       </c>
@@ -6632,7 +6614,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="122" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="122" spans="5:22">
       <c r="E122" t="s">
         <v>165</v>
       </c>
@@ -6653,7 +6635,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="123" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="123" spans="5:22">
       <c r="E123" t="s">
         <v>166</v>
       </c>
@@ -6674,7 +6656,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="124" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="124" spans="5:22">
       <c r="E124" t="s">
         <v>167</v>
       </c>
@@ -6695,7 +6677,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="125" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="125" spans="5:22">
       <c r="E125" t="s">
         <v>168</v>
       </c>
@@ -6716,7 +6698,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="126" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="126" spans="5:22">
       <c r="E126" t="s">
         <v>169</v>
       </c>
@@ -6737,7 +6719,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="127" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="127" spans="5:22">
       <c r="E127" t="s">
         <v>170</v>
       </c>
@@ -6758,7 +6740,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="128" spans="5:22" x14ac:dyDescent="0.3">
+    <row r="128" spans="5:22">
       <c r="E128" t="s">
         <v>171</v>
       </c>
@@ -6779,7 +6761,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="129" spans="18:22" x14ac:dyDescent="0.3">
+    <row r="129" spans="18:22">
       <c r="R129" t="s">
         <v>212</v>
       </c>
@@ -6794,7 +6776,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="130" spans="18:22" x14ac:dyDescent="0.3">
+    <row r="130" spans="18:22">
       <c r="R130" t="s">
         <v>437</v>
       </c>
@@ -6809,7 +6791,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="131" spans="18:22" x14ac:dyDescent="0.3">
+    <row r="131" spans="18:22">
       <c r="R131" t="s">
         <v>440</v>
       </c>
@@ -6824,7 +6806,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="132" spans="18:22" x14ac:dyDescent="0.3">
+    <row r="132" spans="18:22">
       <c r="R132" t="s">
         <v>441</v>
       </c>
@@ -6839,7 +6821,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="133" spans="18:22" x14ac:dyDescent="0.3">
+    <row r="133" spans="18:22">
       <c r="R133" t="s">
         <v>442</v>
       </c>
@@ -6854,7 +6836,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="134" spans="18:22" x14ac:dyDescent="0.3">
+    <row r="134" spans="18:22">
       <c r="R134" t="s">
         <v>213</v>
       </c>
@@ -6869,7 +6851,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="135" spans="18:22" x14ac:dyDescent="0.3">
+    <row r="135" spans="18:22">
       <c r="R135" t="s">
         <v>214</v>
       </c>
@@ -6884,7 +6866,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="136" spans="18:22" x14ac:dyDescent="0.3">
+    <row r="136" spans="18:22">
       <c r="R136" t="s">
         <v>492</v>
       </c>
@@ -6899,7 +6881,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="137" spans="18:22" x14ac:dyDescent="0.3">
+    <row r="137" spans="18:22">
       <c r="R137" t="s">
         <v>271</v>
       </c>
@@ -6914,7 +6896,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="138" spans="18:22" x14ac:dyDescent="0.3">
+    <row r="138" spans="18:22">
       <c r="R138" t="s">
         <v>268</v>
       </c>
@@ -6929,7 +6911,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="139" spans="18:22" x14ac:dyDescent="0.3">
+    <row r="139" spans="18:22">
       <c r="R139" t="s">
         <v>486</v>
       </c>
@@ -6944,7 +6926,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="140" spans="18:22" x14ac:dyDescent="0.3">
+    <row r="140" spans="18:22">
       <c r="R140" t="s">
         <v>489</v>
       </c>
@@ -6959,7 +6941,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="141" spans="18:22" x14ac:dyDescent="0.3">
+    <row r="141" spans="18:22">
       <c r="R141" t="s">
         <v>490</v>
       </c>
@@ -6974,7 +6956,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="142" spans="18:22" x14ac:dyDescent="0.3">
+    <row r="142" spans="18:22">
       <c r="R142" t="s">
         <v>491</v>
       </c>
@@ -6989,7 +6971,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="143" spans="18:22" x14ac:dyDescent="0.3">
+    <row r="143" spans="18:22">
       <c r="R143" t="s">
         <v>269</v>
       </c>
@@ -7004,7 +6986,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="144" spans="18:22" x14ac:dyDescent="0.3">
+    <row r="144" spans="18:22">
       <c r="R144" t="s">
         <v>270</v>
       </c>
@@ -7019,7 +7001,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="145" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="145" spans="21:22">
       <c r="U145" t="s">
         <v>204</v>
       </c>
@@ -7027,7 +7009,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="146" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="146" spans="21:22">
       <c r="U146" t="s">
         <v>205</v>
       </c>
@@ -7035,7 +7017,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="147" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="147" spans="21:22">
       <c r="U147" t="s">
         <v>206</v>
       </c>
@@ -7043,7 +7025,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="148" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="148" spans="21:22">
       <c r="U148" t="s">
         <v>207</v>
       </c>
@@ -7051,7 +7033,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="149" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="149" spans="21:22">
       <c r="U149" t="s">
         <v>208</v>
       </c>
@@ -7059,7 +7041,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="150" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="150" spans="21:22">
       <c r="U150" t="s">
         <v>209</v>
       </c>
@@ -7067,7 +7049,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="151" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="151" spans="21:22">
       <c r="U151" t="s">
         <v>210</v>
       </c>
@@ -7075,7 +7057,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="152" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="152" spans="21:22">
       <c r="U152" t="s">
         <v>211</v>
       </c>
@@ -7083,7 +7065,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="153" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="153" spans="21:22">
       <c r="U153" t="s">
         <v>212</v>
       </c>
@@ -7091,7 +7073,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="154" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="154" spans="21:22">
       <c r="U154" t="s">
         <v>213</v>
       </c>
@@ -7099,7 +7081,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="155" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="155" spans="21:22">
       <c r="U155" t="s">
         <v>214</v>
       </c>
@@ -7107,7 +7089,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="156" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="156" spans="21:22">
       <c r="U156" t="s">
         <v>215</v>
       </c>
@@ -7115,7 +7097,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="157" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="157" spans="21:22">
       <c r="U157" t="s">
         <v>216</v>
       </c>
@@ -7123,7 +7105,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="158" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="158" spans="21:22">
       <c r="U158" t="s">
         <v>217</v>
       </c>
@@ -7131,7 +7113,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="159" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="159" spans="21:22">
       <c r="U159" t="s">
         <v>218</v>
       </c>
@@ -7139,7 +7121,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="160" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="160" spans="21:22">
       <c r="U160" t="s">
         <v>219</v>
       </c>
@@ -7147,7 +7129,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="161" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="161" spans="21:22">
       <c r="U161" t="s">
         <v>220</v>
       </c>
@@ -7155,7 +7137,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="162" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="162" spans="21:22">
       <c r="U162" t="s">
         <v>221</v>
       </c>
@@ -7163,7 +7145,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="163" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="163" spans="21:22">
       <c r="U163" t="s">
         <v>222</v>
       </c>
@@ -7171,7 +7153,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="164" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="164" spans="21:22">
       <c r="U164" t="s">
         <v>223</v>
       </c>
@@ -7179,7 +7161,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="165" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="165" spans="21:22">
       <c r="U165" t="s">
         <v>224</v>
       </c>
@@ -7187,7 +7169,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="166" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="166" spans="21:22">
       <c r="U166" t="s">
         <v>225</v>
       </c>
@@ -7195,7 +7177,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="167" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="167" spans="21:22">
       <c r="U167" t="s">
         <v>226</v>
       </c>
@@ -7203,7 +7185,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="168" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="168" spans="21:22">
       <c r="U168" t="s">
         <v>227</v>
       </c>
@@ -7211,7 +7193,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="169" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="169" spans="21:22">
       <c r="U169" t="s">
         <v>228</v>
       </c>
@@ -7219,7 +7201,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="170" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="170" spans="21:22">
       <c r="U170" t="s">
         <v>229</v>
       </c>
@@ -7227,7 +7209,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="171" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="171" spans="21:22">
       <c r="U171" t="s">
         <v>230</v>
       </c>
@@ -7235,7 +7217,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="172" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="172" spans="21:22">
       <c r="U172" t="s">
         <v>231</v>
       </c>
@@ -7243,7 +7225,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="173" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="173" spans="21:22">
       <c r="U173" t="s">
         <v>232</v>
       </c>
@@ -7251,7 +7233,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="174" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="174" spans="21:22">
       <c r="U174" t="s">
         <v>233</v>
       </c>
@@ -7259,7 +7241,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="175" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="175" spans="21:22">
       <c r="U175" t="s">
         <v>234</v>
       </c>
@@ -7267,7 +7249,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="176" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="176" spans="21:22">
       <c r="U176" t="s">
         <v>235</v>
       </c>
@@ -7275,7 +7257,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="177" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="177" spans="21:22">
       <c r="U177" t="s">
         <v>236</v>
       </c>
@@ -7283,7 +7265,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="178" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="178" spans="21:22">
       <c r="U178" t="s">
         <v>237</v>
       </c>
@@ -7291,7 +7273,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="179" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="179" spans="21:22">
       <c r="U179" t="s">
         <v>238</v>
       </c>
@@ -7299,7 +7281,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="180" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="180" spans="21:22">
       <c r="U180" t="s">
         <v>239</v>
       </c>
@@ -7307,7 +7289,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="181" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="181" spans="21:22">
       <c r="U181" t="s">
         <v>240</v>
       </c>
@@ -7315,7 +7297,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="182" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="182" spans="21:22">
       <c r="U182" t="s">
         <v>241</v>
       </c>
@@ -7323,7 +7305,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="183" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="183" spans="21:22">
       <c r="U183" t="s">
         <v>242</v>
       </c>
@@ -7331,7 +7313,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="184" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="184" spans="21:22">
       <c r="U184" t="s">
         <v>243</v>
       </c>
@@ -7339,7 +7321,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="185" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="185" spans="21:22">
       <c r="U185" t="s">
         <v>244</v>
       </c>
@@ -7347,7 +7329,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="186" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="186" spans="21:22">
       <c r="U186" t="s">
         <v>245</v>
       </c>
@@ -7355,7 +7337,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="187" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="187" spans="21:22">
       <c r="U187" t="s">
         <v>246</v>
       </c>
@@ -7363,7 +7345,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="188" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="188" spans="21:22">
       <c r="U188" t="s">
         <v>247</v>
       </c>
@@ -7371,7 +7353,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="189" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="189" spans="21:22">
       <c r="U189" t="s">
         <v>248</v>
       </c>
@@ -7379,7 +7361,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="190" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="190" spans="21:22">
       <c r="U190" t="s">
         <v>249</v>
       </c>
@@ -7387,7 +7369,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="191" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="191" spans="21:22">
       <c r="U191" t="s">
         <v>250</v>
       </c>
@@ -7395,7 +7377,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="192" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="192" spans="21:22">
       <c r="U192" t="s">
         <v>251</v>
       </c>
@@ -7403,7 +7385,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="193" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="193" spans="21:22">
       <c r="U193" t="s">
         <v>252</v>
       </c>
@@ -7411,7 +7393,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="194" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="194" spans="21:22">
       <c r="U194" t="s">
         <v>253</v>
       </c>
@@ -7419,7 +7401,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="195" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="195" spans="21:22">
       <c r="U195" t="s">
         <v>254</v>
       </c>
@@ -7427,7 +7409,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="196" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="196" spans="21:22">
       <c r="U196" t="s">
         <v>255</v>
       </c>
@@ -7435,7 +7417,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="197" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="197" spans="21:22">
       <c r="U197" t="s">
         <v>256</v>
       </c>
@@ -7443,7 +7425,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="198" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="198" spans="21:22">
       <c r="U198" t="s">
         <v>257</v>
       </c>
@@ -7451,7 +7433,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="199" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="199" spans="21:22">
       <c r="U199" t="s">
         <v>258</v>
       </c>
@@ -7459,7 +7441,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="200" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="200" spans="21:22">
       <c r="U200" t="s">
         <v>259</v>
       </c>
@@ -7467,7 +7449,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="201" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="201" spans="21:22">
       <c r="U201" t="s">
         <v>260</v>
       </c>
@@ -7475,7 +7457,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="202" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="202" spans="21:22">
       <c r="U202" t="s">
         <v>261</v>
       </c>
@@ -7483,7 +7465,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="203" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="203" spans="21:22">
       <c r="U203" t="s">
         <v>262</v>
       </c>
@@ -7491,7 +7473,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="204" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="204" spans="21:22">
       <c r="U204" t="s">
         <v>263</v>
       </c>
@@ -7499,7 +7481,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="205" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="205" spans="21:22">
       <c r="U205" t="s">
         <v>264</v>
       </c>
@@ -7507,7 +7489,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="206" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="206" spans="21:22">
       <c r="U206" t="s">
         <v>265</v>
       </c>
@@ -7515,7 +7497,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="207" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="207" spans="21:22">
       <c r="U207" t="s">
         <v>266</v>
       </c>
@@ -7523,7 +7505,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="208" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="208" spans="21:22">
       <c r="U208" t="s">
         <v>267</v>
       </c>
@@ -7531,7 +7513,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="209" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="209" spans="21:22">
       <c r="U209" t="s">
         <v>268</v>
       </c>
@@ -7539,7 +7521,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="210" spans="21:22">
       <c r="U210" t="s">
         <v>269</v>
       </c>
@@ -7547,7 +7529,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="211" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="211" spans="21:22">
       <c r="U211" t="s">
         <v>270</v>
       </c>
@@ -7555,7 +7537,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="212" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="212" spans="21:22">
       <c r="U212" t="s">
         <v>271</v>
       </c>
@@ -7563,7 +7545,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="213" spans="21:22">
       <c r="U213" t="s">
         <v>272</v>
       </c>
@@ -7571,7 +7553,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="214" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="214" spans="21:22">
       <c r="U214" t="s">
         <v>273</v>
       </c>
@@ -7579,7 +7561,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="215" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="215" spans="21:22">
       <c r="U215" t="s">
         <v>274</v>
       </c>
@@ -7587,7 +7569,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="216" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="216" spans="21:22">
       <c r="U216" t="s">
         <v>275</v>
       </c>
@@ -7595,7 +7577,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="217" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="217" spans="21:22">
       <c r="U217" t="s">
         <v>276</v>
       </c>
@@ -7603,7 +7585,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="218" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="218" spans="21:22">
       <c r="U218" t="s">
         <v>277</v>
       </c>
@@ -7611,7 +7593,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="219" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="219" spans="21:22">
       <c r="U219" t="s">
         <v>278</v>
       </c>
@@ -7619,7 +7601,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="220" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="220" spans="21:22">
       <c r="U220" t="s">
         <v>279</v>
       </c>
@@ -7627,7 +7609,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="221" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="221" spans="21:22">
       <c r="U221" t="s">
         <v>280</v>
       </c>
@@ -7635,7 +7617,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="222" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="222" spans="21:22">
       <c r="U222" t="s">
         <v>281</v>
       </c>
@@ -7643,7 +7625,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="223" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="223" spans="21:22">
       <c r="U223" t="s">
         <v>282</v>
       </c>
@@ -7651,7 +7633,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="224" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="224" spans="21:22">
       <c r="U224" t="s">
         <v>283</v>
       </c>
@@ -7659,7 +7641,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="225" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="225" spans="21:22">
       <c r="U225" t="s">
         <v>284</v>
       </c>
@@ -7667,7 +7649,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="226" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="226" spans="21:22">
       <c r="U226" t="s">
         <v>285</v>
       </c>
@@ -7675,7 +7657,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="227" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="227" spans="21:22">
       <c r="U227" t="s">
         <v>286</v>
       </c>
@@ -7683,7 +7665,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="228" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="228" spans="21:22">
       <c r="U228" t="s">
         <v>287</v>
       </c>
@@ -7691,7 +7673,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="229" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="229" spans="21:22">
       <c r="U229" t="s">
         <v>288</v>
       </c>
@@ -7699,7 +7681,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="230" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="230" spans="21:22">
       <c r="U230" t="s">
         <v>289</v>
       </c>
@@ -7707,7 +7689,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="231" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="231" spans="21:22">
       <c r="U231" t="s">
         <v>290</v>
       </c>
@@ -7715,7 +7697,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="232" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="232" spans="21:22">
       <c r="U232" t="s">
         <v>291</v>
       </c>
@@ -7723,7 +7705,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="233" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="233" spans="21:22">
       <c r="U233" t="s">
         <v>292</v>
       </c>
@@ -7731,7 +7713,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="234" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="234" spans="21:22">
       <c r="U234" t="s">
         <v>293</v>
       </c>
@@ -7739,7 +7721,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="235" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="235" spans="21:22">
       <c r="U235" t="s">
         <v>294</v>
       </c>
@@ -7747,7 +7729,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="236" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="236" spans="21:22">
       <c r="U236" t="s">
         <v>295</v>
       </c>
@@ -7755,7 +7737,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="237" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="237" spans="21:22">
       <c r="U237" t="s">
         <v>296</v>
       </c>
@@ -7763,7 +7745,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="238" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="238" spans="21:22">
       <c r="U238" t="s">
         <v>297</v>
       </c>
@@ -7771,7 +7753,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="239" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="239" spans="21:22">
       <c r="U239" t="s">
         <v>298</v>
       </c>
@@ -7779,7 +7761,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="240" spans="21:22" x14ac:dyDescent="0.3">
+    <row r="240" spans="21:22">
       <c r="U240" t="s">
         <v>299</v>
       </c>
